--- a/Outputs/Scenarios/PtX_demand_DK_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DK_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0004952914075622283</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002597802445510831</v>
+        <v>0.002877396064777138</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0005781945420258964</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.005195604891021662</v>
+        <v>0.004625556336207171</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>3.969274576932214e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.003620701055041954</v>
+        <v>0.003620701055041953</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0002402602736480331</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03518777503476935</v>
+        <v>0.03518777503476934</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>7.136310795228682e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0008659341485036104</v>
+        <v>0.0005781945420258964</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0007332186289504282</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01400067233614843</v>
+        <v>0.01550752234985518</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.003116138543730626</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.02800134467229687</v>
+        <v>0.02492910834984501</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>3.85904541552857e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.004666890778716145</v>
+        <v>0.003116138543730626</v>
       </c>
     </row>
     <row r="43">
